--- a/docs/Decodifiche/158_dmnm_dec_tipo_filiaz.xlsx
+++ b/docs/Decodifiche/158_dmnm_dec_tipo_filiaz.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>(Legittima)</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:20.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>(Da entrambi i genitori)</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:23:21.0</t>
   </si>
   <si>
     <t>5</t>
@@ -210,7 +207,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -221,19 +218,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
